--- a/.cursor/scratch/tax_turbo_parts/216 N Oak Park Ave.xlsx
+++ b/.cursor/scratch/tax_turbo_parts/216 N Oak Park Ave.xlsx
@@ -30,7 +30,7 @@
       <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -40,6 +40,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="001F4E79"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C6EFCE"/>
       </patternFill>
     </fill>
     <fill>
@@ -65,13 +70,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -559,13 +565,13 @@
       <c r="J3" s="2" t="n">
         <v>2450</v>
       </c>
-      <c r="K3" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L3" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M3" s="2" t="n">
+      <c r="K3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" s="3" t="n">
         <v>0</v>
       </c>
       <c r="N3" s="2" t="n">
@@ -761,40 +767,40 @@
           <t>MARKETING / ADVERTISING</t>
         </is>
       </c>
-      <c r="C8" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D8" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E8" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F8" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G8" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H8" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I8" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J8" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M8" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N8" s="3" t="n">
+      <c r="C8" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" s="4" t="n">
         <v>0</v>
       </c>
       <c r="O8">
@@ -808,40 +814,40 @@
           <t>SERVICE FEES</t>
         </is>
       </c>
-      <c r="C9" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D9" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E9" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G9" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H9" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I9" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J9" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K9" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M9" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N9" s="3" t="n">
+      <c r="C9" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" s="4" t="n">
         <v>0</v>
       </c>
       <c r="O9">
@@ -855,40 +861,40 @@
           <t>REMITTED TAX</t>
         </is>
       </c>
-      <c r="C10" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D10" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E10" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G10" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H10" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I10" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J10" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M10" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" s="3" t="n">
+      <c r="C10" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" s="4" t="n">
         <v>0</v>
       </c>
       <c r="O10">
@@ -902,40 +908,40 @@
           <t>INSURANCE</t>
         </is>
       </c>
-      <c r="C11" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D11" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E11" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F11" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G11" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H11" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I11" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J11" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M11" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N11" s="3" t="n">
+      <c r="C11" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D11" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" s="4" t="n">
         <v>0</v>
       </c>
       <c r="O11">
@@ -982,8 +988,8 @@
       <c r="M12" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="N12" s="3" t="n">
-        <v>0</v>
+      <c r="N12" s="2" t="n">
+        <v>675</v>
       </c>
       <c r="O12">
         <f>SUM(C12:N12)</f>
@@ -996,40 +1002,40 @@
           <t>EXTERIOR REPAIRS</t>
         </is>
       </c>
-      <c r="C13" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D13" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E13" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F13" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G13" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H13" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I13" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J13" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M13" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" s="3" t="n">
+      <c r="C13" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" s="4" t="n">
         <v>0</v>
       </c>
       <c r="O13">
@@ -1043,40 +1049,40 @@
           <t>VILLAGE WATER AND REFUSE</t>
         </is>
       </c>
-      <c r="C14" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D14" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E14" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F14" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G14" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H14" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I14" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J14" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M14" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N14" s="3" t="n">
+      <c r="C14" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D14" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" s="4" t="n">
         <v>0</v>
       </c>
       <c r="O14">
@@ -1090,40 +1096,40 @@
           <t>GAS</t>
         </is>
       </c>
-      <c r="C15" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D15" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E15" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F15" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G15" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H15" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I15" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J15" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M15" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" s="3" t="n">
+      <c r="C15" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D15" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" s="4" t="n">
         <v>0</v>
       </c>
       <c r="O15">
@@ -1137,40 +1143,40 @@
           <t>ELECTRIC</t>
         </is>
       </c>
-      <c r="C16" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D16" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E16" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F16" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G16" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H16" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I16" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J16" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K16" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M16" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N16" s="3" t="n">
+      <c r="C16" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D16" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" s="4" t="n">
         <v>0</v>
       </c>
       <c r="O16">
@@ -1184,40 +1190,40 @@
           <t>INTERNET</t>
         </is>
       </c>
-      <c r="C17" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D17" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E17" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F17" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G17" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H17" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I17" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J17" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M17" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N17" s="3" t="n">
+      <c r="C17" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D17" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" s="4" t="n">
         <v>0</v>
       </c>
       <c r="O17">
@@ -1231,40 +1237,40 @@
           <t>CLEANING / TURNOVER</t>
         </is>
       </c>
-      <c r="C18" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D18" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E18" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F18" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G18" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H18" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I18" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J18" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M18" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N18" s="3" t="n">
+      <c r="C18" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D18" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" s="4" t="n">
         <v>0</v>
       </c>
       <c r="O18">
@@ -1278,40 +1284,40 @@
           <t>SUPPLIES</t>
         </is>
       </c>
-      <c r="C19" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D19" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E19" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F19" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G19" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H19" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I19" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J19" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K19" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M19" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N19" s="3" t="n">
+      <c r="C19" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D19" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E19" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" s="4" t="n">
         <v>0</v>
       </c>
       <c r="O19">
@@ -1325,40 +1331,40 @@
           <t>EQUIPMENT/APPLIANCE PURCHASES</t>
         </is>
       </c>
-      <c r="C20" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D20" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E20" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F20" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G20" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H20" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I20" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J20" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K20" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L20" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M20" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N20" s="3" t="n">
+      <c r="C20" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D20" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E20" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" s="4" t="n">
         <v>0</v>
       </c>
       <c r="O20">
@@ -1372,40 +1378,40 @@
           <t>LAND TAX</t>
         </is>
       </c>
-      <c r="C21" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D21" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E21" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F21" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G21" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H21" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I21" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J21" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K21" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M21" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N21" s="3" t="n">
+      <c r="C21" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D21" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E21" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J21" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" s="4" t="n">
         <v>0</v>
       </c>
       <c r="O21">
@@ -1419,40 +1425,40 @@
           <t>LOANS INTEREST (from 1098)</t>
         </is>
       </c>
-      <c r="C22" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D22" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E22" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F22" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G22" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H22" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I22" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J22" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K22" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L22" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M22" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N22" s="3" t="n">
+      <c r="C22" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D22" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E22" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F22" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J22" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N22" s="4" t="n">
         <v>0</v>
       </c>
       <c r="O22">
@@ -1484,22 +1490,22 @@
       <c r="H23" t="n">
         <v>0</v>
       </c>
-      <c r="I23" s="4" t="n">
+      <c r="I23" s="5" t="n">
         <v>1226.25</v>
       </c>
-      <c r="J23" s="4" t="n">
+      <c r="J23" s="5" t="n">
         <v>1226.25</v>
       </c>
-      <c r="K23" s="4" t="n">
+      <c r="K23" s="5" t="n">
         <v>1226.25</v>
       </c>
-      <c r="L23" s="4" t="n">
+      <c r="L23" s="5" t="n">
         <v>1226.25</v>
       </c>
-      <c r="M23" s="4" t="n">
+      <c r="M23" s="5" t="n">
         <v>1177.52</v>
       </c>
-      <c r="N23" s="4" t="n">
+      <c r="N23" s="5" t="n">
         <v>1177.52</v>
       </c>
       <c r="O23">
@@ -1528,25 +1534,25 @@
       <c r="G24" t="n">
         <v>0</v>
       </c>
-      <c r="H24" s="4" t="n">
+      <c r="H24" s="5" t="n">
         <v>421.53</v>
       </c>
-      <c r="I24" s="4" t="n">
+      <c r="I24" s="5" t="n">
         <v>421.53</v>
       </c>
-      <c r="J24" s="4" t="n">
+      <c r="J24" s="5" t="n">
         <v>421.53</v>
       </c>
-      <c r="K24" s="4" t="n">
+      <c r="K24" s="5" t="n">
         <v>421.53</v>
       </c>
-      <c r="L24" s="4" t="n">
+      <c r="L24" s="5" t="n">
         <v>421.53</v>
       </c>
-      <c r="M24" s="4" t="n">
+      <c r="M24" s="5" t="n">
         <v>421.53</v>
       </c>
-      <c r="N24" s="4" t="n">
+      <c r="N24" s="5" t="n">
         <v>421.53</v>
       </c>
       <c r="O24">
@@ -1560,40 +1566,40 @@
           <t>OTHER</t>
         </is>
       </c>
-      <c r="C25" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D25" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E25" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F25" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G25" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H25" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I25" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J25" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K25" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L25" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M25" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N25" s="3" t="n">
+      <c r="C25" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D25" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E25" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F25" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G25" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H25" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I25" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J25" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L25" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M25" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N25" s="4" t="n">
         <v>0</v>
       </c>
       <c r="O25">
@@ -1722,9 +1728,9 @@
     </row>
     <row r="29"/>
     <row r="30">
-      <c r="B30" s="5" t="inlineStr">
-        <is>
-          <t>LTR rent 2026-09-18: joint 0203 Zelle — Delach $1,450 + Ava $500 (yellow, ASK roommate) Feb–Sep cash, then Joan $1,950 on 12/1 and 12/31 (yellow, ASK Dec vs Jan-2026 prepaid). TY2025 cash $19500.00. Oct–Nov no rent on 0203 (ASK vacancy). Jan 2025 occupancy was paid 12/31/2024 — not in this year. HOA + Rocket payment cash from Monarch (green). Deduct interest from Rocket 1098 only — not full P+I. Not tax advice.</t>
+      <c r="B30" s="6" t="inlineStr">
+        <is>
+          <t>LTR after answers 2026-09-18: Ava CONFIRMED Delach co-tenant — keep $500/mo. TY2025 cash $19500.00 (Delach $11,600 + Ava $4,000 + Joan $3,900). Occupancy vacant October and half of November (held for rent). Joan half-Nov $975 NOT booked — not on 0203, WAIT 8507. 12/1 $1,950 IN = December occupancy cash; 12/31 $1,950 = Jan 2026 prepaid cash in TY2025. 12/1 8507 Zelle OUT $675 to Joan → INTERIOR MAINTENANCE (repair). Jan 2025 occupancy was paid 12/31/2024 — not in this year. HOA + Rocket payment cash from Monarch (green). Deduct interest from Rocket 1098 only — not full P+I. Not tax advice.</t>
         </is>
       </c>
     </row>

--- a/.cursor/scratch/tax_turbo_parts/216 N Oak Park Ave.xlsx
+++ b/.cursor/scratch/tax_turbo_parts/216 N Oak Park Ave.xlsx
@@ -257,7 +257,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="43">
+  <cellXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -368,13 +368,10 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="10" fontId="15" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="15" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="16" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="16" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="17" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -739,7 +736,6 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="FFFFC000"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
@@ -2284,41 +2280,41 @@
         <f>SUM(P14:AA14)</f>
         <v/>
       </c>
-      <c r="AC14" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD14" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE14" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF14" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG14" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH14" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI14" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ14" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK14" s="16" t="n">
-        <v>0</v>
+      <c r="AC14" s="28" t="n">
+        <v>42.84</v>
+      </c>
+      <c r="AD14" s="28" t="n">
+        <v>42.84</v>
+      </c>
+      <c r="AE14" s="28" t="n">
+        <v>42.84</v>
+      </c>
+      <c r="AF14" s="28" t="n">
+        <v>42.84</v>
+      </c>
+      <c r="AG14" s="28" t="n">
+        <v>42.84</v>
+      </c>
+      <c r="AH14" s="28" t="n">
+        <v>42.84</v>
+      </c>
+      <c r="AI14" s="28" t="n">
+        <v>42.84</v>
+      </c>
+      <c r="AJ14" s="28" t="n">
+        <v>42.84</v>
+      </c>
+      <c r="AK14" s="28" t="n">
+        <v>42.84</v>
       </c>
       <c r="AL14" s="28" t="n">
-        <v>514</v>
-      </c>
-      <c r="AM14" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN14" s="17" t="n">
-        <v>0</v>
+        <v>42.84</v>
+      </c>
+      <c r="AM14" s="28" t="n">
+        <v>42.84</v>
+      </c>
+      <c r="AN14" s="28" t="n">
+        <v>42.84</v>
       </c>
       <c r="AO14" s="18">
         <f>SUM(AC14:AN14)</f>
@@ -2430,8 +2426,8 @@
       <c r="AI15" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="AJ15" s="16" t="n">
-        <v>0</v>
+      <c r="AJ15" s="28" t="n">
+        <v>150</v>
       </c>
       <c r="AK15" s="16" t="n">
         <v>0</v>
@@ -2442,8 +2438,8 @@
       <c r="AM15" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="AN15" s="20" t="n">
-        <v>675</v>
+      <c r="AN15" s="28" t="n">
+        <v>11</v>
       </c>
       <c r="AO15" s="18">
         <f>SUM(AC15:AN15)</f>
@@ -2569,8 +2565,8 @@
       <c r="AM16" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="AN16" s="17" t="n">
-        <v>0</v>
+      <c r="AN16" s="28" t="n">
+        <v>675</v>
       </c>
       <c r="AO16" s="18">
         <f>SUM(AC16:AN16)</f>
@@ -4183,40 +4179,40 @@
         <f>SUM(P29:AA29)</f>
         <v/>
       </c>
-      <c r="AC29" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD29" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE29" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF29" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG29" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH29" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI29" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ29" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK29" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL29" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM29" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN29" s="17" t="n">
+      <c r="AC29" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD29" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE29" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF29" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG29" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH29" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI29" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ29" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK29" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL29" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM29" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN29" s="29" t="n">
         <v>0</v>
       </c>
       <c r="AO29" s="18">
@@ -4946,39 +4942,39 @@
         <v/>
       </c>
       <c r="AC35" s="29" t="n">
-        <v>0</v>
+        <v>1226.25</v>
       </c>
       <c r="AD35" s="29" t="n">
-        <v>0</v>
+        <v>1226.25</v>
       </c>
       <c r="AE35" s="29" t="n">
-        <v>0</v>
+        <v>1226.25</v>
       </c>
       <c r="AF35" s="29" t="n">
-        <v>0</v>
+        <v>1226.25</v>
       </c>
       <c r="AG35" s="29" t="n">
-        <v>0</v>
+        <v>1226.25</v>
       </c>
       <c r="AH35" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI35" s="20" t="n">
         <v>1226.25</v>
       </c>
-      <c r="AJ35" s="20" t="n">
+      <c r="AI35" s="28" t="n">
         <v>1226.25</v>
       </c>
-      <c r="AK35" s="20" t="n">
+      <c r="AJ35" s="28" t="n">
         <v>1226.25</v>
       </c>
-      <c r="AL35" s="20" t="n">
+      <c r="AK35" s="28" t="n">
         <v>1226.25</v>
       </c>
-      <c r="AM35" s="20" t="n">
+      <c r="AL35" s="28" t="n">
+        <v>1226.25</v>
+      </c>
+      <c r="AM35" s="28" t="n">
         <v>1177.52</v>
       </c>
-      <c r="AN35" s="20" t="n">
+      <c r="AN35" s="28" t="n">
         <v>1177.52</v>
       </c>
       <c r="AO35" s="18">
@@ -5073,39 +5069,39 @@
         <v/>
       </c>
       <c r="AC36" s="29" t="n">
-        <v>0</v>
+        <v>421.53</v>
       </c>
       <c r="AD36" s="29" t="n">
-        <v>0</v>
+        <v>421.53</v>
       </c>
       <c r="AE36" s="29" t="n">
-        <v>0</v>
+        <v>421.53</v>
       </c>
       <c r="AF36" s="29" t="n">
-        <v>0</v>
+        <v>421.53</v>
       </c>
       <c r="AG36" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH36" s="20" t="n">
         <v>421.53</v>
       </c>
-      <c r="AI36" s="20" t="n">
+      <c r="AH36" s="28" t="n">
         <v>421.53</v>
       </c>
-      <c r="AJ36" s="20" t="n">
+      <c r="AI36" s="28" t="n">
         <v>421.53</v>
       </c>
-      <c r="AK36" s="20" t="n">
+      <c r="AJ36" s="28" t="n">
         <v>421.53</v>
       </c>
-      <c r="AL36" s="20" t="n">
+      <c r="AK36" s="28" t="n">
         <v>421.53</v>
       </c>
-      <c r="AM36" s="20" t="n">
+      <c r="AL36" s="28" t="n">
         <v>421.53</v>
       </c>
-      <c r="AN36" s="20" t="n">
+      <c r="AM36" s="28" t="n">
+        <v>421.53</v>
+      </c>
+      <c r="AN36" s="28" t="n">
         <v>421.53</v>
       </c>
       <c r="AO36" s="18">
@@ -5349,8 +5345,8 @@
       <c r="AK38" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="AL38" s="17" t="n">
-        <v>0</v>
+      <c r="AL38" s="28" t="n">
+        <v>300</v>
       </c>
       <c r="AM38" s="17" t="n">
         <v>0</v>
@@ -6171,63 +6167,63 @@
     <row r="60">
       <c r="B60" s="40" t="inlineStr">
         <is>
-          <t>2025 (this column)</t>
+          <t>2025 (this column) — user cost list LOCKED 2026-09-20, last-year Excel pattern.</t>
         </is>
       </c>
     </row>
     <row r="61">
-      <c r="B61" s="41" t="inlineStr">
-        <is>
-          <t>Rent — filled from joint 0203 (Delach $1,450 + Ava $500; Joan $1,950 Dec + prepaid Jan). Vacant Oct + half Nov. Half-Nov $975 WAIT 8507.</t>
+      <c r="B61" s="40" t="inlineStr">
+        <is>
+          <t>Rent — joint 0203 (Delach $1,450 + Ava $500; Joan $1,950 Dec + prepaid Jan). Vacant Oct + half Nov. Half-Nov $975 WAIT 8507.</t>
         </is>
       </c>
     </row>
     <row r="62">
-      <c r="B62" s="41" t="inlineStr">
-        <is>
-          <t>Mortgage — Rocket 8507 Jul–Oct $1,226.25, Nov–Dec $1,177.52. Jan–Jun yellow WAIT 8507 statements (June 8507 in Monarch has no Rocket).</t>
+      <c r="B62" s="40" t="inlineStr">
+        <is>
+          <t>Mortgage — user $1,226.25/mo. Cash 8507 Jul–Oct $1,226.25 / Nov–Dec $1,177.52 (green). Jan–Jun $1,226.25 yellow WAIT 8507 (not on Monarch). Sch E uses Rocket 1098 interest, not full P+I.</t>
         </is>
       </c>
     </row>
     <row r="63">
-      <c r="B63" s="41" t="inlineStr">
-        <is>
-          <t>HOA — Santa Maria C326 $421.53 Jun–Dec on 8507. Jan–May yellow WAIT 8507.</t>
+      <c r="B63" s="40" t="inlineStr">
+        <is>
+          <t>HOA — user $421.53/mo Santa Maria C326. Jun–Dec cash 8507 green. Jan–May $421.53 yellow WAIT 8507.</t>
         </is>
       </c>
     </row>
     <row r="64">
-      <c r="B64" s="42" t="inlineStr">
-        <is>
-          <t>LOCKED 2026-09-20: 216 LTR insurance = Lemonade $514.00 cash 10/3 on Megan Chase (1702). Same annual Oct 3 Lemonade as 2023 $321 (= Excel $26.75/mo renter's) and 2024 $421 (≈ Excel $35.08/mo renter's). 2025 books cash in October (not amortized). Travelers = prior 524 Ferdinand home (not 216). Geico = cars. State Farm 2025 bundle = Ferdinand car+home — only home share on 524, not 216. No other Oak Park policy cash on Prime/Sapphire/BoA/0203/8507/Monarch. Not tax advice.</t>
+      <c r="B64" s="40" t="inlineStr">
+        <is>
+          <t>Insurance — user $42.84/mo × 12 = $514.08 on RENTER'S INSURANCE (amortized like 2023 $26.75 / 2024 $35.08). Lemonade cash $514.00 10/3 Megan Chase (8¢). Not Travelers/Geico/State Farm.</t>
         </is>
       </c>
     </row>
     <row r="65">
-      <c r="B65" s="41" t="inlineStr">
-        <is>
-          <t>Interior — 12/1 Zelle to Joan $675 repair (CONFIRMED). CPA may reclass interior vs exterior.</t>
+      <c r="B65" s="40" t="inlineStr">
+        <is>
+          <t>Interior — Chris Brennan exterminator $150 8/7 (8507 check posted 8/18) INTERIOR Aug. Ace keys $11 12/8 Megan Chase INTERIOR Dec. Same-day Ace $17 not booked.</t>
         </is>
       </c>
     </row>
     <row r="66">
-      <c r="B66" s="41" t="inlineStr">
-        <is>
-          <t>Sch E: deduct Rocket 1098 interest, not full P+I. This sheet shows cash mortgage like 2023/2024.</t>
+      <c r="B66" s="40" t="inlineStr">
+        <is>
+          <t>Interior repair — Joan $675 12/1 8507 Zelle painting + repairs → INTERIOR REPAIR December (2024 used this row for Oak Park painting).</t>
         </is>
       </c>
     </row>
     <row r="67">
-      <c r="B67" s="41" t="inlineStr">
-        <is>
-          <t>Jan 2025 occupancy cash hit 12/31/2024 — not in TY2025. 12/31/2025 $1,950 = Jan 2026 prepaid cash in TY2025.</t>
+      <c r="B67" s="40" t="inlineStr">
+        <is>
+          <t>Move-out — Imelda $300 empty-apt. User 9/30; cash 10/1 joint 0203 → MOVE OUT FEE October (same month as 2023/24 $200). Other 2025 Imelda $150s not on 216.</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="B68" s="41" t="inlineStr">
         <is>
-          <t>Not tax advice.</t>
+          <t>Smoke detector Amazon — still ASK (checklist TBD). No Kidde/First Alert/detector SKU on Monarch/Prime/Sapphire/BoA. EQUIPMENT yellow $0. Not tax advice.</t>
         </is>
       </c>
     </row>
